--- a/output/Data and Chart Outputs/singapore_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/singapore_power_generation_daily.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Units" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart - Demand" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demand" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Units" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Chart" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Chart - Demand" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Daily" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Demand" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,8 +21,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="164" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -62,10 +62,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -143,18 +144,19 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Singapore power generation by type (EMC / NEMS metered) (to Sep/26)</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>Singapore power generation by type (EMC / NEMS metered) (to Aug/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -174,22 +176,22 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="2A78D6"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$70</f>
+              <f>'Chart'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$70</f>
+              <f>'Chart'!$B$2:$B$69</f>
             </numRef>
           </val>
         </ser>
@@ -202,22 +204,22 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="EB6834"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$70</f>
+              <f>'Chart'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$70</f>
+              <f>'Chart'!$C$2:$C$69</f>
             </numRef>
           </val>
         </ser>
@@ -230,22 +232,22 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1BAF7A"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$70</f>
+              <f>'Chart'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$70</f>
+              <f>'Chart'!$D$2:$D$69</f>
             </numRef>
           </val>
         </ser>
@@ -258,22 +260,22 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="EDA100"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$70</f>
+              <f>'Chart'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$70</f>
+              <f>'Chart'!$E$2:$E$69</f>
             </numRef>
           </val>
         </ser>
@@ -286,22 +288,22 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="E87BA4"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$70</f>
+              <f>'Chart'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$70</f>
+              <f>'Chart'!$F$2:$F$69</f>
             </numRef>
           </val>
         </ser>
@@ -314,22 +316,22 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="008300"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$70</f>
+              <f>'Chart'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$70</f>
+              <f>'Chart'!$G$2:$G$69</f>
             </numRef>
           </val>
         </ser>
@@ -342,22 +344,22 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="9A9A9A"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$70</f>
+              <f>'Chart'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$70</f>
+              <f>'Chart'!$H$2:$H$69</f>
             </numRef>
           </val>
         </ser>
@@ -378,8 +380,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-2700000" vert="horz"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -405,8 +407,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -423,7 +425,7 @@
         <crossAx val="10"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -437,7 +439,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -446,17 +448,18 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Singapore system demand (EMA) (to Sep/26)</a:t>
             </a:r>
           </a:p>
@@ -476,7 +479,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22225">
+            <a:ln w="22225">
               <a:solidFill>
                 <a:srgbClr val="2A78D6"/>
               </a:solidFill>
@@ -486,7 +489,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -512,7 +515,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22225">
+            <a:ln w="22225">
               <a:solidFill>
                 <a:srgbClr val="EB6834"/>
               </a:solidFill>
@@ -522,7 +525,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -554,8 +557,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-2700000" vert="horz"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -581,8 +584,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -599,7 +602,7 @@
         <crossAx val="10"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -613,7 +616,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -622,7 +625,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>9</col>
@@ -637,9 +640,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -649,7 +652,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -664,9 +667,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -998,7 +1001,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -1020,7 +1022,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
@@ -1035,7 +1036,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1131,7 +1131,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -1157,7 +1157,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -1183,7 +1183,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -1209,7 +1209,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -1235,7 +1235,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -1261,7 +1261,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -1287,7 +1287,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -1313,7 +1313,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -1339,7 +1339,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -1365,7 +1365,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -1391,7 +1391,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -1417,7 +1417,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -1443,7 +1443,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -1469,7 +1469,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -1495,7 +1495,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -1521,7 +1521,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -1547,7 +1547,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -1573,7 +1573,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -1599,7 +1599,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -1625,7 +1625,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -1651,7 +1651,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -1677,7 +1677,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -1703,7 +1703,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -1729,7 +1729,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -1755,7 +1755,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -1781,7 +1781,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -1807,7 +1807,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -1833,7 +1833,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -1859,7 +1859,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -1885,7 +1885,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -1911,7 +1911,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -1937,7 +1937,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -1963,7 +1963,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -1989,7 +1989,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -2015,7 +2015,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -2041,7 +2041,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -2067,7 +2067,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -2093,7 +2093,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -2119,7 +2119,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -2145,7 +2145,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -2171,7 +2171,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -2197,7 +2197,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -2223,7 +2223,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -2249,7 +2249,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -2275,7 +2275,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -2301,7 +2301,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -2327,7 +2327,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -2353,7 +2353,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -2379,7 +2379,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -2405,7 +2405,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -2431,7 +2431,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -2457,7 +2457,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -2483,7 +2483,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -2509,7 +2509,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -2535,7 +2535,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -2561,7 +2561,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -2587,7 +2587,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -2613,7 +2613,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -2639,7 +2639,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -2665,7 +2665,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -2691,7 +2691,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -2717,7 +2717,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -2743,7 +2743,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -2769,7 +2769,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -2795,7 +2795,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -2821,7 +2821,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -2847,7 +2847,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -2873,7 +2873,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B69" t="n">
@@ -2896,32 +2896,6 @@
       </c>
       <c r="H69" t="n">
         <v>217.414</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B70" t="n">
-        <v>0</v>
-      </c>
-      <c r="C70" t="n">
-        <v>3280.678</v>
-      </c>
-      <c r="D70" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" t="n">
-        <v>145.569</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="n">
-        <v>139.687</v>
       </c>
     </row>
   </sheetData>
@@ -2960,7 +2934,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -2971,84 +2945,84 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
-        <v>6118.628571428571</v>
+        <v>6118.62857142857</v>
       </c>
       <c r="C3" t="n">
         <v>6750.05</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
-        <v>6343.200000000001</v>
+        <v>6343.2</v>
       </c>
       <c r="C4" t="n">
-        <v>7030.551612903226</v>
+        <v>7030.551612903227</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
-        <v>6409.91</v>
+        <v>6409.910000000001</v>
       </c>
       <c r="C5" t="n">
         <v>7091.236666666667</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
-        <v>6432.874193548388</v>
+        <v>6432.874193548387</v>
       </c>
       <c r="C6" t="n">
-        <v>7071.267741935483</v>
+        <v>7071.267741935484</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
-        <v>6512.373333333334</v>
+        <v>6512.373333333333</v>
       </c>
       <c r="C7" t="n">
-        <v>7155.39</v>
+        <v>7155.389999999999</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
-        <v>6455.267741935483</v>
+        <v>6455.267741935484</v>
       </c>
       <c r="C8" t="n">
-        <v>7075.774193548387</v>
+        <v>7075.774193548389</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
-        <v>6321.222580645162</v>
+        <v>6321.22258064516</v>
       </c>
       <c r="C9" t="n">
-        <v>6922.674193548387</v>
+        <v>6922.674193548385</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -3059,172 +3033,172 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
-        <v>6522.203225806451</v>
+        <v>6522.203225806452</v>
       </c>
       <c r="C11" t="n">
-        <v>7153.170967741935</v>
+        <v>7153.170967741936</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
-        <v>6443.486666666667</v>
+        <v>6443.486666666666</v>
       </c>
       <c r="C12" t="n">
         <v>7090.46</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
         <v>6474.935483870968</v>
       </c>
       <c r="C13" t="n">
-        <v>7100.122580645161</v>
+        <v>7100.122580645162</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
-        <v>6397.164516129033</v>
+        <v>6397.164516129032</v>
       </c>
       <c r="C14" t="n">
         <v>7029.796774193549</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
-        <v>6345.621428571429</v>
+        <v>6345.62142857143</v>
       </c>
       <c r="C15" t="n">
         <v>6966.846428571429</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
-        <v>6535.674193548387</v>
+        <v>6535.674193548388</v>
       </c>
       <c r="C16" t="n">
-        <v>7237.251612903226</v>
+        <v>7237.251612903225</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
-        <v>6530.97</v>
+        <v>6530.969999999999</v>
       </c>
       <c r="C17" t="n">
         <v>7176.179999999999</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
         <v>6674.464516129032</v>
       </c>
       <c r="C18" t="n">
-        <v>7331.012903225806</v>
+        <v>7331.012903225807</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
         <v>6544.956666666667</v>
       </c>
       <c r="C19" t="n">
-        <v>7161.446666666667</v>
+        <v>7161.446666666668</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
         <v>6652.016129032259</v>
       </c>
       <c r="C20" t="n">
-        <v>7285.296774193549</v>
+        <v>7285.296774193548</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
-        <v>6592.716129032258</v>
+        <v>6592.716129032259</v>
       </c>
       <c r="C21" t="n">
         <v>7260.716129032258</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
         <v>6538.636666666667</v>
       </c>
       <c r="C22" t="n">
-        <v>7176.03</v>
+        <v>7176.030000000001</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
-        <v>6416.719354838709</v>
+        <v>6416.719354838711</v>
       </c>
       <c r="C23" t="n">
         <v>7055.509677419354</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
-        <v>6495.443333333333</v>
+        <v>6495.443333333334</v>
       </c>
       <c r="C24" t="n">
-        <v>7163.496666666667</v>
+        <v>7163.496666666668</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
-        <v>6253.299999999999</v>
+        <v>6253.3</v>
       </c>
       <c r="C25" t="n">
-        <v>6859.712903225806</v>
+        <v>6859.712903225807</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -3235,18 +3209,18 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
-        <v>6292.724999999999</v>
+        <v>6292.725000000001</v>
       </c>
       <c r="C27" t="n">
         <v>6919.735714285714</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -3257,18 +3231,18 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
-        <v>6596.966666666666</v>
+        <v>6596.966666666665</v>
       </c>
       <c r="C29" t="n">
         <v>7210.113333333333</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -3279,40 +3253,40 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
         <v>6710.436666666666</v>
       </c>
       <c r="C31" t="n">
-        <v>7316.676666666666</v>
+        <v>7316.676666666667</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
         <v>6614.325806451613</v>
       </c>
       <c r="C32" t="n">
-        <v>7220.606451612903</v>
+        <v>7220.606451612904</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
-        <v>6644.235483870967</v>
+        <v>6644.235483870969</v>
       </c>
       <c r="C33" t="n">
-        <v>7276.861290322581</v>
+        <v>7276.86129032258</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -3323,51 +3297,51 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
-        <v>6737.712903225806</v>
+        <v>6737.712903225807</v>
       </c>
       <c r="C35" t="n">
-        <v>7399.648387096774</v>
+        <v>7399.648387096775</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
         <v>6561.11</v>
       </c>
       <c r="C36" t="n">
-        <v>7229.376666666666</v>
+        <v>7229.376666666667</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
-        <v>6351.877419354839</v>
+        <v>6351.877419354838</v>
       </c>
       <c r="C37" t="n">
-        <v>6984.622580645161</v>
+        <v>6984.622580645162</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
-        <v>6458.419354838709</v>
+        <v>6458.41935483871</v>
       </c>
       <c r="C38" t="n">
-        <v>7115.977419354838</v>
+        <v>7115.977419354837</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -3378,139 +3352,139 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
-        <v>6799.783870967742</v>
+        <v>6799.783870967743</v>
       </c>
       <c r="C40" t="n">
         <v>7433.574193548387</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
-        <v>6950.683333333333</v>
+        <v>6950.683333333334</v>
       </c>
       <c r="C41" t="n">
-        <v>7601.03</v>
+        <v>7601.030000000001</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
-        <v>6926</v>
+        <v>6926.000000000001</v>
       </c>
       <c r="C42" t="n">
         <v>7595.645161290323</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
-        <v>6802.693333333333</v>
+        <v>6802.693333333334</v>
       </c>
       <c r="C43" t="n">
         <v>7421.04</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
-        <v>6964.345161290323</v>
+        <v>6964.345161290324</v>
       </c>
       <c r="C44" t="n">
-        <v>7593.103225806452</v>
+        <v>7593.103225806451</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
         <v>6882.125806451612</v>
       </c>
       <c r="C45" t="n">
-        <v>7492.658064516128</v>
+        <v>7492.658064516129</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
-        <v>6857.966666666666</v>
+        <v>6857.966666666665</v>
       </c>
       <c r="C46" t="n">
-        <v>7495.54</v>
+        <v>7495.539999999999</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
-        <v>6839.351612903226</v>
+        <v>6839.351612903225</v>
       </c>
       <c r="C47" t="n">
-        <v>7497.403225806452</v>
+        <v>7497.403225806451</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
         <v>6733.733333333334</v>
       </c>
       <c r="C48" t="n">
-        <v>7374.226666666666</v>
+        <v>7374.226666666667</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
-        <v>6659.122580645161</v>
+        <v>6659.122580645162</v>
       </c>
       <c r="C49" t="n">
-        <v>7251.612903225807</v>
+        <v>7251.612903225805</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
         <v>6478.864516129031</v>
       </c>
       <c r="C50" t="n">
-        <v>7060.067741935484</v>
+        <v>7060.067741935486</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
-        <v>6621.603571428571</v>
+        <v>6621.60357142857</v>
       </c>
       <c r="C51" t="n">
-        <v>7223.889285714286</v>
+        <v>7223.889285714287</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -3521,40 +3495,40 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
-        <v>6832.65</v>
+        <v>6832.650000000001</v>
       </c>
       <c r="C53" t="n">
-        <v>7483.253333333333</v>
+        <v>7483.253333333335</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
-        <v>7085.106451612903</v>
+        <v>7085.106451612904</v>
       </c>
       <c r="C54" t="n">
-        <v>7699.303225806451</v>
+        <v>7699.30322580645</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
         <v>7134.116666666667</v>
       </c>
       <c r="C55" t="n">
-        <v>7748.65</v>
+        <v>7748.649999999999</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -3565,7 +3539,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -3576,62 +3550,62 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
-        <v>6858.62</v>
+        <v>6858.619999999998</v>
       </c>
       <c r="C58" t="n">
-        <v>7470.146666666667</v>
+        <v>7470.146666666666</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
-        <v>6977.725806451613</v>
+        <v>6977.725806451614</v>
       </c>
       <c r="C59" t="n">
         <v>7601.616129032258</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
-        <v>7064.08</v>
+        <v>7064.080000000001</v>
       </c>
       <c r="C60" t="n">
-        <v>7673.906666666667</v>
+        <v>7673.906666666666</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
-        <v>6782.945161290322</v>
+        <v>6782.945161290324</v>
       </c>
       <c r="C61" t="n">
-        <v>7378.845161290323</v>
+        <v>7378.845161290324</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
-        <v>6767.467741935484</v>
+        <v>6767.467741935483</v>
       </c>
       <c r="C62" t="n">
-        <v>7377.964516129032</v>
+        <v>7377.964516129031</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -3642,80 +3616,80 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
-        <v>7067.477419354838</v>
+        <v>7067.477419354837</v>
       </c>
       <c r="C64" t="n">
-        <v>7714.951612903225</v>
+        <v>7714.951612903228</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
         <v>7232.706666666667</v>
       </c>
       <c r="C65" t="n">
-        <v>7915.706666666667</v>
+        <v>7915.706666666666</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
         <v>7197.625806451612</v>
       </c>
       <c r="C66" t="n">
-        <v>7844.474193548387</v>
+        <v>7844.474193548385</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
         <v>7288.323333333334</v>
       </c>
       <c r="C67" t="n">
-        <v>7927.233333333334</v>
+        <v>7927.233333333333</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
         <v>7382.558064516129</v>
       </c>
       <c r="C68" t="n">
-        <v>8033.070967741935</v>
+        <v>8033.070967741937</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B69" t="n">
         <v>7462.664516129033</v>
       </c>
       <c r="C69" t="n">
-        <v>8116.187096774193</v>
+        <v>8116.187096774194</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="3" t="n">
         <v>46266</v>
       </c>
       <c r="B70" t="n">
-        <v>7582.833333333333</v>
+        <v>7582.833333333335</v>
       </c>
       <c r="C70" t="n">
-        <v>8244.766666666666</v>
+        <v>8244.766666666668</v>
       </c>
     </row>
   </sheetData>
